--- a/Job Opening.xlsx
+++ b/Job Opening.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd3e28c50a4aed9d/桌面/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="190" documentId="11_AD4DBB64A54DDB1B405E38F5A5DC1C234E90DF21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A2B7350-5FDF-4B6C-BB7E-71D1CE29FA81}"/>
+  <xr:revisionPtr revIDLastSave="196" documentId="11_AD4DBB64A54DDB1B405E38F5A5DC1C234E90DF21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4478CB72-F951-4BC1-9E8F-836960917164}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>https://reurl.cc/geEmg7</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -363,10 +363,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">軟體研發經理/ 資深經理 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Embedded Linux System Engineer (Network)</t>
   </si>
   <si>
@@ -423,6 +419,55 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> QA</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Embedded Linux System Engineer (MCU)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://reurl.cc/7EvKg1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>軟體研發經理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>資深經理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -548,7 +593,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -575,9 +620,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -868,7 +910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="18.5"/>
   <cols>
     <col min="1" max="1" width="29.5" style="2" customWidth="1"/>
@@ -898,16 +940,16 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="9"/>
-      <c r="B3" s="11" t="s">
-        <v>44</v>
+      <c r="B3" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="B4" s="11" t="s">
-        <v>45</v>
+      <c r="B4" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -997,7 +1039,7 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>35</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -1060,8 +1102,8 @@
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="B25" s="10" t="s">
-        <v>41</v>
+      <c r="B25" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>40</v>
@@ -1069,10 +1111,18 @@
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>43</v>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="B27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1098,8 +1148,9 @@
     <hyperlink ref="C24" r:id="rId18" xr:uid="{F55A4C2D-4C4A-40F5-B340-EFEA62F86853}"/>
     <hyperlink ref="C25" r:id="rId19" xr:uid="{7AB9433D-794D-4EC9-BE8F-2EE1E53FF273}"/>
     <hyperlink ref="C26" r:id="rId20" xr:uid="{FA543E36-EAE9-42BE-8E63-2E4D8E1F5DB8}"/>
+    <hyperlink ref="C27" r:id="rId21" xr:uid="{92D3E564-7601-4C3B-8B6A-10094462042F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>